--- a/test_cases/wscc9.xlsx
+++ b/test_cases/wscc9.xlsx
@@ -12,13 +12,14 @@
     <sheet sheetId="6" name="Area" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="BusROCOF" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="GENCLS" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="TGOV1" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="79">
   <si>
     <t>uid</t>
   </si>
@@ -231,6 +232,30 @@
   </si>
   <si>
     <t>GENCLS_3</t>
+  </si>
+  <si>
+    <t>syn</t>
+  </si>
+  <si>
+    <t>Sg</t>
+  </si>
+  <si>
+    <t>wref0</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>VMAX</t>
+  </si>
+  <si>
+    <t>VMIN</t>
+  </si>
+  <si>
+    <t>TGOV1_2</t>
+  </si>
+  <si>
+    <t>TGOV1_3</t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F2">
         <v>16.5</v>
@@ -3405,10 +3430,10 @@
         <v>60</v>
       </c>
       <c r="K2" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L2" s="4">
-        <v>7.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -3441,10 +3466,10 @@
         <v>60</v>
       </c>
       <c r="K3" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L3" s="4">
-        <v>7.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -3468,7 +3493,7 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="4">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="I4" s="4">
         <v>16.5</v>
@@ -3477,10 +3502,10 @@
         <v>60</v>
       </c>
       <c r="K4" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4">
-        <v>7.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -3515,4 +3540,150 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="4">
+        <v>250</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="J2" s="2">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="4">
+        <v>100</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="J4" s="4">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/test_cases/wscc9.xlsx
+++ b/test_cases/wscc9.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="82">
   <si>
     <t>uid</t>
   </si>
@@ -207,6 +207,12 @@
     <t>Line_8</t>
   </si>
   <si>
+    <t>Tf</t>
+  </si>
+  <si>
+    <t>Tw</t>
+  </si>
+  <si>
     <t>BusROCOF_1</t>
   </si>
   <si>
@@ -250,6 +256,9 @@
   </si>
   <si>
     <t>VMIN</t>
+  </si>
+  <si>
+    <t>Dt</t>
   </si>
   <si>
     <t>TGOV1_2</t>
@@ -2297,8 +2306,12 @@
       <c r="D1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2320,19 +2333,23 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="E2" s="2">
+        <v>0.001</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.001</v>
+      </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -2354,19 +2371,23 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D3" s="2">
         <v>5</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="E3" s="2">
+        <v>0.001</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.001</v>
+      </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -3379,10 +3400,10 @@
         <v>23</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>29</v>
@@ -3394,10 +3415,10 @@
         <v>39</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -3405,13 +3426,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E2" s="4">
         <v>2</v>
@@ -3441,13 +3462,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" s="4">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E3" s="4">
         <v>3</v>
@@ -3477,13 +3498,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
@@ -3544,13 +3565,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3564,39 +3585,42 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="F2" s="4">
         <v>250</v>
@@ -3605,13 +3629,16 @@
         <v>1</v>
       </c>
       <c r="H2" s="4">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I2" s="4">
         <v>1.2</v>
       </c>
       <c r="J2" s="2">
         <v>-0.5</v>
+      </c>
+      <c r="K2">
+        <v>0.8</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -3626,21 +3653,21 @@
       <c r="I3" s="4"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F4" s="4">
         <v>100</v>
@@ -3649,13 +3676,16 @@
         <v>1</v>
       </c>
       <c r="H4" s="4">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I4" s="4">
         <v>1.2</v>
       </c>
       <c r="J4" s="4">
         <v>-0.5</v>
+      </c>
+      <c r="K4">
+        <v>0.8</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
